--- a/Results_experiment/exp_1/preds_1111144422222222.xlsx
+++ b/Results_experiment/exp_1/preds_1111144422222222.xlsx
@@ -924,7 +924,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D2">
-        <v>-4.077839374542236</v>
+        <v>-3.653037786483765</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -938,7 +938,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D3">
-        <v>1.512038826942444</v>
+        <v>1.684815168380737</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -952,7 +952,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D4">
-        <v>0.08545520901679993</v>
+        <v>0.1346142590045929</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -966,7 +966,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D5">
-        <v>1.066465377807617</v>
+        <v>0.6084492206573486</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -980,7 +980,7 @@
         <v>-0.5</v>
       </c>
       <c r="D6">
-        <v>1.075275659561157</v>
+        <v>1.169045805931091</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -994,7 +994,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D7">
-        <v>0.2590403258800507</v>
+        <v>0.353875458240509</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1008,7 +1008,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D8">
-        <v>-0.4080963730812073</v>
+        <v>-0.8784823417663574</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1022,7 +1022,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D9">
-        <v>-3.560776472091675</v>
+        <v>-3.601926565170288</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1036,7 +1036,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D10">
-        <v>0.6013197898864746</v>
+        <v>0.4014350473880768</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1050,7 +1050,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D11">
-        <v>-2.135614156723022</v>
+        <v>-1.889896392822266</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1064,7 +1064,7 @@
         <v>-1.5</v>
       </c>
       <c r="D12">
-        <v>3.459974527359009</v>
+        <v>4.682056903839111</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1078,7 +1078,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D13">
-        <v>0.2573867738246918</v>
+        <v>0.7165722846984863</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1092,7 +1092,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D14">
-        <v>-2.79552960395813</v>
+        <v>-2.986782789230347</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1106,7 +1106,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D15">
-        <v>-1.983598470687866</v>
+        <v>-2.337634801864624</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1120,7 +1120,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D16">
-        <v>-4.067283630371094</v>
+        <v>-2.157493352890015</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1134,7 +1134,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D17">
-        <v>-4.172536849975586</v>
+        <v>-3.15837836265564</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1148,7 +1148,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D18">
-        <v>-5.21564769744873</v>
+        <v>-4.473745822906494</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1162,7 +1162,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D19">
-        <v>-0.20962755382061</v>
+        <v>0.2396048903465271</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1176,7 +1176,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D20">
-        <v>0.3172414600849152</v>
+        <v>0.2484321296215057</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1190,7 +1190,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D21">
-        <v>6.358395576477051</v>
+        <v>8.913253784179688</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1204,7 +1204,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D22">
-        <v>-3.359515905380249</v>
+        <v>-2.000157356262207</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1218,7 +1218,7 @@
         <v>0.5</v>
       </c>
       <c r="D23">
-        <v>-2.562043428421021</v>
+        <v>-1.978665351867676</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1232,7 +1232,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D24">
-        <v>-0.805324912071228</v>
+        <v>-1.764053821563721</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1246,7 +1246,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D25">
-        <v>-0.9329911470413208</v>
+        <v>-2.199673175811768</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1260,7 +1260,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D26">
-        <v>-2.734203577041626</v>
+        <v>-3.233423948287964</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1274,7 +1274,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D27">
-        <v>-2.191852807998657</v>
+        <v>-2.332546949386597</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1288,7 +1288,7 @@
         <v>4</v>
       </c>
       <c r="D28">
-        <v>1.004752039909363</v>
+        <v>0.9542092084884644</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1302,7 +1302,7 @@
         <v>-5.5</v>
       </c>
       <c r="D29">
-        <v>-3.699284315109253</v>
+        <v>-3.501945734024048</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1316,7 +1316,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D30">
-        <v>-0.9005402326583862</v>
+        <v>-0.9671097993850708</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1330,7 +1330,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D31">
-        <v>-3.830238580703735</v>
+        <v>-3.715878963470459</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1344,7 +1344,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D32">
-        <v>0.1964779198169708</v>
+        <v>0.2388462722301483</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1358,7 +1358,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D33">
-        <v>0.6322370767593384</v>
+        <v>0.369408518075943</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1372,7 +1372,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D34">
-        <v>0.5777653455734253</v>
+        <v>0.8878847360610962</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1386,7 +1386,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D35">
-        <v>-3.441962480545044</v>
+        <v>-2.407150030136108</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1400,7 +1400,7 @@
         <v>-7.5</v>
       </c>
       <c r="D36">
-        <v>-3.270357370376587</v>
+        <v>-2.978955507278442</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1414,7 +1414,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D37">
-        <v>-1.76875901222229</v>
+        <v>-1.7876136302948</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>-3.505025625228882</v>
+        <v>-2.625567197799683</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1442,7 +1442,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D39">
-        <v>0.9883302450180054</v>
+        <v>1.066373348236084</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1456,7 +1456,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D40">
-        <v>0.6837167739868164</v>
+        <v>0.4950523972511292</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1470,7 +1470,7 @@
         <v>11.60000038146973</v>
       </c>
       <c r="D41">
-        <v>2.281973123550415</v>
+        <v>1.629871845245361</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1484,7 +1484,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D42">
-        <v>0.5348037481307983</v>
+        <v>0.3315083682537079</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1498,7 +1498,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D43">
-        <v>-1.762208342552185</v>
+        <v>-1.622715830802917</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1512,7 +1512,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D44">
-        <v>-5.515885353088379</v>
+        <v>-4.557287216186523</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1526,7 +1526,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D45">
-        <v>1.105582594871521</v>
+        <v>0.8795394897460938</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1540,7 +1540,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D46">
-        <v>0.9619351625442505</v>
+        <v>0.5163965821266174</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1554,7 +1554,7 @@
         <v>-6.800000190734863</v>
       </c>
       <c r="D47">
-        <v>-6.263592720031738</v>
+        <v>-4.709616661071777</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1568,7 +1568,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D48">
-        <v>1.471139669418335</v>
+        <v>1.621710538864136</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1582,7 +1582,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D49">
-        <v>-2.37232232093811</v>
+        <v>-2.581987619400024</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1596,7 +1596,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D50">
-        <v>-3.822725057601929</v>
+        <v>-3.467288732528687</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D51">
-        <v>-0.3234657049179077</v>
+        <v>-0.07614999264478683</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>23.29999923706055</v>
       </c>
       <c r="D52">
-        <v>16.11165237426758</v>
+        <v>18.10863876342773</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1638,7 +1638,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D53">
-        <v>0.8313446044921875</v>
+        <v>0.589788556098938</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D54">
-        <v>1.438517093658447</v>
+        <v>2.838582754135132</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1666,7 +1666,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D55">
-        <v>0.2928033173084259</v>
+        <v>0.6543468832969666</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D56">
-        <v>1.004858732223511</v>
+        <v>1.02882719039917</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1694,7 +1694,7 @@
         <v>2.5</v>
       </c>
       <c r="D57">
-        <v>1.491827249526978</v>
+        <v>2.565386533737183</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D58">
-        <v>-3.832746267318726</v>
+        <v>-4.43326473236084</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D59">
-        <v>-3.969182729721069</v>
+        <v>-3.471259117126465</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1736,7 +1736,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D60">
-        <v>0.1850646138191223</v>
+        <v>0.2842698693275452</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D61">
-        <v>2.338230133056641</v>
+        <v>2.419691562652588</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D62">
-        <v>0.1436106264591217</v>
+        <v>-0.6124173998832703</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1778,7 +1778,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D63">
-        <v>-4.321374893188477</v>
+        <v>-3.413957357406616</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1792,7 +1792,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D64">
-        <v>1.615102410316467</v>
+        <v>1.470830202102661</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1806,7 +1806,7 @@
         <v>-1</v>
       </c>
       <c r="D65">
-        <v>0.9129617214202881</v>
+        <v>1.413120746612549</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1820,7 +1820,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D66">
-        <v>1.439312219619751</v>
+        <v>0.7890716195106506</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D67">
-        <v>-3.280096292495728</v>
+        <v>-3.358909845352173</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D68">
-        <v>0.1192524135112762</v>
+        <v>-0.1342258900403976</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>-11.19999980926514</v>
       </c>
       <c r="D69">
-        <v>-8.689591407775879</v>
+        <v>-7.545704364776611</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>0.6215804815292358</v>
+        <v>0.4971612691879272</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D71">
-        <v>-1.720916509628296</v>
+        <v>-1.681972503662109</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1904,7 +1904,7 @@
         <v>-2</v>
       </c>
       <c r="D72">
-        <v>0.2503274083137512</v>
+        <v>0.621251106262207</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1918,7 +1918,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D73">
-        <v>1.195026278495789</v>
+        <v>0.9569393396377563</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D74">
-        <v>0.3867795765399933</v>
+        <v>-0.02942676842212677</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D75">
-        <v>0.3344624936580658</v>
+        <v>-0.202735424041748</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1960,7 +1960,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D76">
-        <v>-3.93337607383728</v>
+        <v>-2.951251268386841</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1974,7 +1974,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D77">
-        <v>-0.20808345079422</v>
+        <v>-0.533309280872345</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D78">
-        <v>0.7602177858352661</v>
+        <v>-0.9800369143486023</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D79">
-        <v>1.876424312591553</v>
+        <v>0.9437090158462524</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D80">
-        <v>-0.1815212666988373</v>
+        <v>-0.7512369155883789</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D81">
-        <v>-0.03911000490188599</v>
+        <v>0.03334151953458786</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D82">
-        <v>0.4971314370632172</v>
+        <v>0.5112594366073608</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D83">
-        <v>-0.3385606408119202</v>
+        <v>-0.2684347629547119</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>-6</v>
       </c>
       <c r="D84">
-        <v>-6.379302024841309</v>
+        <v>-5.927931308746338</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>0.5</v>
       </c>
       <c r="D85">
-        <v>1.381628751754761</v>
+        <v>1.870556592941284</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D86">
-        <v>1.319541454315186</v>
+        <v>2.111472606658936</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D87">
-        <v>-4.426914215087891</v>
+        <v>-3.853960275650024</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D88">
-        <v>0.2860089838504791</v>
+        <v>0.6311779022216797</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D89">
-        <v>-1.131330966949463</v>
+        <v>0.2270331084728241</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D90">
-        <v>-3.810542106628418</v>
+        <v>-3.658969402313232</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D91">
-        <v>-6.463480472564697</v>
+        <v>-6.488333225250244</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D92">
-        <v>-2.130414962768555</v>
+        <v>-0.9417570233345032</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D93">
-        <v>-3.841155290603638</v>
+        <v>-2.314593553543091</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D94">
-        <v>-1.963933229446411</v>
+        <v>-0.9887537360191345</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D95">
-        <v>0.07479700446128845</v>
+        <v>-0.493482232093811</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D96">
-        <v>0.1865091323852539</v>
+        <v>0.702420711517334</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D97">
-        <v>-3.932043790817261</v>
+        <v>-3.024056434631348</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D98">
-        <v>-6.317004203796387</v>
+        <v>-7.089996814727783</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D99">
-        <v>-9.629456520080566</v>
+        <v>-8.482830047607422</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D100">
-        <v>0.4159886538982391</v>
+        <v>0.567749559879303</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D101">
-        <v>-8.476706504821777</v>
+        <v>-5.917254447937012</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D102">
-        <v>-0.02342325448989868</v>
+        <v>0.3274940550327301</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D103">
-        <v>0.6049213409423828</v>
+        <v>0.6307238340377808</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D104">
-        <v>3.933273077011108</v>
+        <v>4.450025081634521</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D105">
-        <v>0.5133405923843384</v>
+        <v>1.020442366600037</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D106">
-        <v>0.04905900359153748</v>
+        <v>0.4400689005851746</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>-11.39999961853027</v>
       </c>
       <c r="D107">
-        <v>-9.030111312866211</v>
+        <v>-8.605330467224121</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D108">
-        <v>1.112949848175049</v>
+        <v>1.401928067207336</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D109">
-        <v>-4.221779823303223</v>
+        <v>-3.620702981948853</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D110">
-        <v>-2.846712350845337</v>
+        <v>-2.860857725143433</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D111">
-        <v>-2.524410009384155</v>
+        <v>-2.54693865776062</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D112">
-        <v>0.7714403867721558</v>
+        <v>0.9420366287231445</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D113">
-        <v>-1.688600778579712</v>
+        <v>-1.662539720535278</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D114">
-        <v>-4.70061206817627</v>
+        <v>-3.961080312728882</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D115">
-        <v>1.37890350818634</v>
+        <v>1.195117950439453</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>-2</v>
       </c>
       <c r="D116">
-        <v>0.473444789648056</v>
+        <v>0.7613714933395386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D117">
-        <v>0.6438958644866943</v>
+        <v>0.5894718170166016</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D118">
-        <v>0.779988169670105</v>
+        <v>0.6317306160926819</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>-5.5</v>
       </c>
       <c r="D119">
-        <v>-3.647058963775635</v>
+        <v>-2.544152975082397</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D120">
-        <v>0.9194217920303345</v>
+        <v>0.9587812423706055</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D121">
-        <v>0.5043925046920776</v>
+        <v>0.9217572808265686</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D122">
-        <v>2.663352727890015</v>
+        <v>2.58440899848938</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D123">
-        <v>-2.066869258880615</v>
+        <v>-1.457826614379883</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>-6</v>
       </c>
       <c r="D124">
-        <v>-3.23835015296936</v>
+        <v>-2.031850814819336</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D125">
-        <v>1.146432042121887</v>
+        <v>1.001938581466675</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>-3.5</v>
       </c>
       <c r="D126">
-        <v>-2.263122797012329</v>
+        <v>-1.877691507339478</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D127">
-        <v>-10.09564685821533</v>
+        <v>-11.48837757110596</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D128">
-        <v>0.812873363494873</v>
+        <v>0.8103849291801453</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D129">
-        <v>-3.005165100097656</v>
+        <v>-3.403913259506226</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D130">
-        <v>0.2985220849514008</v>
+        <v>0.829859733581543</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D131">
-        <v>1.819988489151001</v>
+        <v>1.757108688354492</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="D132">
-        <v>1.039881229400635</v>
+        <v>1.142588973045349</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D133">
-        <v>-3.385383605957031</v>
+        <v>-2.984904050827026</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D134">
-        <v>2.081993341445923</v>
+        <v>1.425055265426636</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>2.5</v>
       </c>
       <c r="D135">
-        <v>0.760197639465332</v>
+        <v>0.8516802787780762</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D136">
-        <v>4.505452632904053</v>
+        <v>6.437263965606689</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D137">
-        <v>1.413413763046265</v>
+        <v>1.085342645645142</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D138">
-        <v>0.417244166135788</v>
+        <v>0.4144197702407837</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D139">
-        <v>0.312945693731308</v>
+        <v>0.1057508215308189</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D140">
-        <v>3.455448865890503</v>
+        <v>3.328243732452393</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>-14.5</v>
       </c>
       <c r="D141">
-        <v>-2.850887298583984</v>
+        <v>-3.420828819274902</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D142">
-        <v>-1.802096843719482</v>
+        <v>-0.4519992768764496</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D143">
-        <v>-0.5810489654541016</v>
+        <v>-0.06232937425374985</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D144">
-        <v>0.4208166301250458</v>
+        <v>-0.831944465637207</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D145">
-        <v>-0.8671009540557861</v>
+        <v>-0.9485059976577759</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>-12</v>
       </c>
       <c r="D146">
-        <v>-10.29707527160645</v>
+        <v>-10.73072910308838</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>-12.5</v>
       </c>
       <c r="D147">
-        <v>-8.908621788024902</v>
+        <v>-8.103419303894043</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2968,7 +2968,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D148">
-        <v>-0.4222726225852966</v>
+        <v>-0.8148443102836609</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>0.3313997089862823</v>
+        <v>-0.160036712884903</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2996,7 +2996,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D150">
-        <v>0.3464936912059784</v>
+        <v>0.229141891002655</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3010,7 +3010,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D151">
-        <v>1.21001672744751</v>
+        <v>0.9845254421234131</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>1.5</v>
       </c>
       <c r="D152">
-        <v>0.9056302309036255</v>
+        <v>0.863537073135376</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3038,7 +3038,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D153">
-        <v>1.639221906661987</v>
+        <v>2.416627645492554</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3052,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="D154">
-        <v>1.905148267745972</v>
+        <v>1.780020236968994</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>-6.800000190734863</v>
       </c>
       <c r="D155">
-        <v>-5.634044647216797</v>
+        <v>-4.527091503143311</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D156">
-        <v>1.395037770271301</v>
+        <v>2.277791738510132</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D157">
-        <v>0.1576602160930634</v>
+        <v>0.4324039220809937</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3108,7 +3108,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D158">
-        <v>2.547117948532104</v>
+        <v>3.076313495635986</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3122,7 +3122,7 @@
         <v>-9.5</v>
       </c>
       <c r="D159">
-        <v>-4.970684051513672</v>
+        <v>-4.66401481628418</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3136,7 +3136,7 @@
         <v>-5.5</v>
       </c>
       <c r="D160">
-        <v>-1.917606234550476</v>
+        <v>-2.287896394729614</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D161">
-        <v>2.099249124526978</v>
+        <v>1.855164885520935</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3164,7 +3164,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D162">
-        <v>1.223247766494751</v>
+        <v>1.3922119140625</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3178,7 +3178,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D163">
-        <v>0.372586578130722</v>
+        <v>1.219948291778564</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3192,7 +3192,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D164">
-        <v>1.061367034912109</v>
+        <v>1.224309682846069</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3206,7 +3206,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D165">
-        <v>2.036426782608032</v>
+        <v>1.848331212997437</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3220,7 +3220,7 @@
         <v>-3</v>
       </c>
       <c r="D166">
-        <v>-0.50807785987854</v>
+        <v>-0.03909912705421448</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D167">
-        <v>-4.270780563354492</v>
+        <v>-4.067778587341309</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D168">
-        <v>0.7532532215118408</v>
+        <v>0.6957838535308838</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3262,7 +3262,7 @@
         <v>2</v>
       </c>
       <c r="D169">
-        <v>1.131552457809448</v>
+        <v>1.368345260620117</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3276,7 +3276,7 @@
         <v>-5</v>
       </c>
       <c r="D170">
-        <v>0.8871452808380127</v>
+        <v>0.683635950088501</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D171">
-        <v>-1.962528944015503</v>
+        <v>-2.329744100570679</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3304,7 +3304,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D172">
-        <v>-2.983680963516235</v>
+        <v>-2.883821725845337</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3318,7 +3318,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D173">
-        <v>-1.254368662834167</v>
+        <v>-1.22618567943573</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D174">
-        <v>3.736749887466431</v>
+        <v>3.067395448684692</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3346,7 +3346,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D175">
-        <v>-0.01971036195755005</v>
+        <v>0.3860971629619598</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>1.5</v>
       </c>
       <c r="D176">
-        <v>0.1183347702026367</v>
+        <v>0.3530522584915161</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3374,7 +3374,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D177">
-        <v>0.2092312276363373</v>
+        <v>0.7294250726699829</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3388,7 +3388,7 @@
         <v>-3.5</v>
       </c>
       <c r="D178">
-        <v>0.5843478441238403</v>
+        <v>0.3734440803527832</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D179">
-        <v>-2.076652050018311</v>
+        <v>-1.331361770629883</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3416,7 +3416,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D180">
-        <v>1.163866758346558</v>
+        <v>2.636839151382446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3430,7 +3430,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D181">
-        <v>1.999418973922729</v>
+        <v>2.317891597747803</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3444,7 +3444,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D182">
-        <v>-5.570140361785889</v>
+        <v>-5.272477626800537</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3458,7 +3458,7 @@
         <v>-1.5</v>
       </c>
       <c r="D183">
-        <v>-3.686996221542358</v>
+        <v>-3.166626453399658</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3472,7 +3472,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D184">
-        <v>-7.232143402099609</v>
+        <v>-6.705241680145264</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3486,7 +3486,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D185">
-        <v>-0.1023978963494301</v>
+        <v>-1.235734105110168</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3500,7 +3500,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D186">
-        <v>1.26223611831665</v>
+        <v>-0.8816949129104614</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3514,7 +3514,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D187">
-        <v>-0.7032750844955444</v>
+        <v>-0.7852947115898132</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3528,7 +3528,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D188">
-        <v>0.2196316123008728</v>
+        <v>0.106824092566967</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3542,7 +3542,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D189">
-        <v>-2.293598890304565</v>
+        <v>-2.178471088409424</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D190">
-        <v>-0.6923682689666748</v>
+        <v>-0.2892411947250366</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3570,7 +3570,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D191">
-        <v>0.6641356945037842</v>
+        <v>0.5786401033401489</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3584,7 +3584,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D192">
-        <v>-6.070394039154053</v>
+        <v>-5.718391895294189</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3598,7 +3598,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D193">
-        <v>-4.112736225128174</v>
+        <v>-3.354562997817993</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3612,7 +3612,7 @@
         <v>-2.5</v>
       </c>
       <c r="D194">
-        <v>0.4389431178569794</v>
+        <v>0.7903213500976562</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3626,7 +3626,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D195">
-        <v>-1.408964157104492</v>
+        <v>-1.818578004837036</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3640,7 +3640,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D196">
-        <v>0.2052055597305298</v>
+        <v>0.5917686820030212</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3654,7 +3654,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D197">
-        <v>0.3140614926815033</v>
+        <v>0.5924542546272278</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3668,7 +3668,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D198">
-        <v>1.854567527770996</v>
+        <v>2.042463302612305</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3682,7 +3682,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D199">
-        <v>-4.934922218322754</v>
+        <v>-4.7582106590271</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3696,7 +3696,7 @@
         <v>2.5</v>
       </c>
       <c r="D200">
-        <v>1.745147228240967</v>
+        <v>1.678630590438843</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>2.5</v>
       </c>
       <c r="D201">
-        <v>-5.187952041625977</v>
+        <v>-4.12548303604126</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3724,7 +3724,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D202">
-        <v>4.033122062683105</v>
+        <v>4.986531734466553</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D203">
-        <v>0.8440454006195068</v>
+        <v>1.0837562084198</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3752,7 +3752,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D204">
-        <v>-1.192538142204285</v>
+        <v>-0.7543962001800537</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3766,7 +3766,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D205">
-        <v>0.3110474050045013</v>
+        <v>0.1859544813632965</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3780,7 +3780,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D206">
-        <v>-5.297475814819336</v>
+        <v>-3.426186800003052</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3794,7 +3794,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D207">
-        <v>-0.8379268646240234</v>
+        <v>-3.233139991760254</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3808,7 +3808,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D208">
-        <v>1.214266657829285</v>
+        <v>1.015888690948486</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D209">
-        <v>-9.355578422546387</v>
+        <v>-8.581971168518066</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D210">
-        <v>-2.376091718673706</v>
+        <v>-1.789706468582153</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3850,7 +3850,7 @@
         <v>-1.5</v>
       </c>
       <c r="D211">
-        <v>-5.038511276245117</v>
+        <v>-3.702358722686768</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D212">
-        <v>-0.6473594307899475</v>
+        <v>-0.737721860408783</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3878,7 +3878,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D213">
-        <v>-3.927849769592285</v>
+        <v>-3.951200008392334</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3892,7 +3892,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D214">
-        <v>0.5930759906768799</v>
+        <v>1.191770792007446</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3906,7 +3906,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D215">
-        <v>-2.226919174194336</v>
+        <v>-2.30381178855896</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3920,7 +3920,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D216">
-        <v>-0.3746092617511749</v>
+        <v>-1.156205892562866</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3934,7 +3934,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D217">
-        <v>0.3195018470287323</v>
+        <v>0.2841016948223114</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3948,7 +3948,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D218">
-        <v>0.3577800691127777</v>
+        <v>0.5912895202636719</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>-2.5</v>
       </c>
       <c r="D219">
-        <v>-1.589776039123535</v>
+        <v>-2.201310396194458</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3976,7 +3976,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D220">
-        <v>-2.611521482467651</v>
+        <v>-2.351197957992554</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3990,7 +3990,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D221">
-        <v>-0.7907696962356567</v>
+        <v>-0.5662668347358704</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4004,7 +4004,7 @@
         <v>-3.5</v>
       </c>
       <c r="D222">
-        <v>0.2385330498218536</v>
+        <v>0.2823934555053711</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4018,7 +4018,7 @@
         <v>-6</v>
       </c>
       <c r="D223">
-        <v>-4.247505187988281</v>
+        <v>-4.054564952850342</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4032,7 +4032,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D224">
-        <v>-9.081243515014648</v>
+        <v>-7.486489772796631</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4046,7 +4046,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D225">
-        <v>-3.906975507736206</v>
+        <v>-3.168046236038208</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4060,7 +4060,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D226">
-        <v>0.7860100269317627</v>
+        <v>0.5953835844993591</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4074,7 +4074,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D227">
-        <v>-2.256250143051147</v>
+        <v>-2.17090916633606</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4088,7 +4088,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D228">
-        <v>-3.66314959526062</v>
+        <v>-4.478888034820557</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4102,7 +4102,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D229">
-        <v>3.913965463638306</v>
+        <v>4.607077121734619</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4116,7 +4116,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D230">
-        <v>-5.527710437774658</v>
+        <v>-6.082288265228271</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4130,7 +4130,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D231">
-        <v>-4.218579292297363</v>
+        <v>-4.084374904632568</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4144,7 +4144,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D232">
-        <v>-2.073144197463989</v>
+        <v>-1.600633859634399</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4158,7 +4158,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D233">
-        <v>0.7947762012481689</v>
+        <v>-1.092078685760498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="D234">
-        <v>-3.493484258651733</v>
+        <v>-4.541608333587646</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4186,7 +4186,7 @@
         <v>-4</v>
       </c>
       <c r="D235">
-        <v>0.6125659942626953</v>
+        <v>0.7029120922088623</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4200,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="D236">
-        <v>1.585697412490845</v>
+        <v>2.10102653503418</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4214,7 +4214,7 @@
         <v>8</v>
       </c>
       <c r="D237">
-        <v>2.173600196838379</v>
+        <v>3.214097261428833</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4228,7 +4228,7 @@
         <v>-10</v>
       </c>
       <c r="D238">
-        <v>-10.54950904846191</v>
+        <v>-9.254530906677246</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4242,7 +4242,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D239">
-        <v>-8.491982460021973</v>
+        <v>-7.689050197601318</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4256,7 +4256,7 @@
         <v>19</v>
       </c>
       <c r="D240">
-        <v>16.0369873046875</v>
+        <v>11.69751644134521</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4270,7 +4270,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D241">
-        <v>-0.9012469053268433</v>
+        <v>-0.9175047278404236</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4284,7 +4284,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D242">
-        <v>0.5034514665603638</v>
+        <v>1.436137557029724</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4298,7 +4298,7 @@
         <v>-3</v>
       </c>
       <c r="D243">
-        <v>-0.9600816965103149</v>
+        <v>1.682212710380554</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4312,7 +4312,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D244">
-        <v>-3.512849569320679</v>
+        <v>-2.352719068527222</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4326,7 +4326,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D245">
-        <v>3.14705228805542</v>
+        <v>2.588005065917969</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4340,7 +4340,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D246">
-        <v>0.9920194149017334</v>
+        <v>1.19455361366272</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4354,7 +4354,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D247">
-        <v>-8.104473114013672</v>
+        <v>-6.74547290802002</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4368,7 +4368,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D248">
-        <v>1.008350968360901</v>
+        <v>0.9348262548446655</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>8</v>
       </c>
       <c r="D249">
-        <v>2.716195344924927</v>
+        <v>2.498608350753784</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4396,7 +4396,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D250">
-        <v>-10.40496158599854</v>
+        <v>-9.401970863342285</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4410,7 +4410,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D251">
-        <v>-1.449938178062439</v>
+        <v>-2.256737947463989</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4424,7 +4424,7 @@
         <v>-7</v>
       </c>
       <c r="D252">
-        <v>-4.482419013977051</v>
+        <v>-4.442359447479248</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4438,7 +4438,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D253">
-        <v>-6.958251953125</v>
+        <v>-5.224280834197998</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4452,7 +4452,7 @@
         <v>0.5</v>
       </c>
       <c r="D254">
-        <v>0.5943396091461182</v>
+        <v>0.6881163120269775</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4466,7 +4466,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D255">
-        <v>-0.1082701832056046</v>
+        <v>0.3781215846538544</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4480,7 +4480,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D256">
-        <v>-7.50178861618042</v>
+        <v>-4.947828769683838</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4494,7 +4494,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D257">
-        <v>0.9962525367736816</v>
+        <v>1.202932119369507</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D258">
-        <v>-2.623517274856567</v>
+        <v>-2.058300495147705</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4522,7 +4522,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D259">
-        <v>-0.1130906268954277</v>
+        <v>0.08613481372594833</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4536,7 +4536,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D260">
-        <v>-0.07917165011167526</v>
+        <v>0.2871168553829193</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4550,7 +4550,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D261">
-        <v>0.2774621546268463</v>
+        <v>0.2341208457946777</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4564,7 +4564,7 @@
         <v>-7.699999809265137</v>
       </c>
       <c r="D262">
-        <v>-1.054723024368286</v>
+        <v>-1.239266514778137</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D263">
-        <v>-1.868496656417847</v>
+        <v>-1.263037919998169</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D264">
-        <v>0.004074856638908386</v>
+        <v>-0.6999063491821289</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4606,7 +4606,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D265">
-        <v>1.052128553390503</v>
+        <v>1.18036937713623</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4620,7 +4620,7 @@
         <v>-10.19999980926514</v>
       </c>
       <c r="D266">
-        <v>-6.872440338134766</v>
+        <v>-6.477061748504639</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4634,7 +4634,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D267">
-        <v>2.247538328170776</v>
+        <v>2.568859338760376</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4648,7 +4648,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D268">
-        <v>1.34369969367981</v>
+        <v>1.550106763839722</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4662,7 +4662,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D269">
-        <v>-1.762395143508911</v>
+        <v>-0.4950062334537506</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4676,7 +4676,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D270">
-        <v>-1.638776540756226</v>
+        <v>-1.523618459701538</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4690,7 +4690,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D271">
-        <v>0.4608559906482697</v>
+        <v>0.6840607523918152</v>
       </c>
     </row>
   </sheetData>
